--- a/docs/prd/DayLink-화면목록-IA-v2.3.xlsx
+++ b/docs/prd/DayLink-화면목록-IA-v2.3.xlsx
@@ -5640,7 +5640,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -6000,7 +5999,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -6467,7 +6465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6491,7 +6489,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -6691,6 +6688,57 @@
       <c r="E11" s="14" t="inlineStr">
         <is>
           <t>렌더링 전략과 색인 정책이 정책 문서와 동일해 경로만 늘어남. B2C-HELP-002가 흡수하며 slug 목록은 about·terms·privacy·cancellation 넷으로 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v2.3 → v2.4 (2026-08-31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>회차 화면 경로 5건</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/partner/sessions → /partner/slots, /desk/sessions → /desk/slots (scan·manual 포함)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ADR-0014 회차 엔터티 Session → Slot 개명. 06 §8.6의 인증 세션과 이름이 겹쳐 JVM에서 HttpSession과 구분이 어려움</t>
         </is>
       </c>
     </row>
